--- a/data/satisfaction_detail/2026/6月/参会人员.xlsx
+++ b/data/satisfaction_detail/2026/6月/参会人员.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>9.93</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.67</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.94</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.56</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.56</v>
+        <v>9.58</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="15">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>10</v>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9.83</v>
+        <v>9.91</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.94</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.94</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="19">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.56</v>
+        <v>9.52</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>10</v>
